--- a/Data terbaru dip/X5 Persentase Perempuan Lulus Wajib Belajar/X6 Jumlah Lulus 2020.xlsx
+++ b/Data terbaru dip/X5 Persentase Perempuan Lulus Wajib Belajar/X6 Jumlah Lulus 2020.xlsx
@@ -1,26 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KULIAH\Project\womanguard-index-surabaya\Data terbaru dip\X5 Persentase Perempuan Lulus Wajib Belajar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{946D39C7-CE5B-4937-8D28-A740ADE72EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D7DFEB7-F5C8-40CA-B2D5-A969BE6DC6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17580" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Pendidikan 2024" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="45">
   <si>
     <t>Kecamatan
 Subdistrict</t>
@@ -62,10 +73,6 @@
   <si>
     <t>S3
 Doctor</t>
-  </si>
-  <si>
-    <t>Jumlah
-Total</t>
   </si>
   <si>
     <t>Laki-Laki
@@ -618,18 +625,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V36"/>
+  <dimension ref="A1:U36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="21" width="13" customWidth="1"/>
-    <col min="22" max="22" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="25.05" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" ht="25.05" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
     </row>
-    <row r="3" spans="1:22" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>0</v>
       </c>
@@ -673,77 +679,73 @@
         <v>10</v>
       </c>
       <c r="U3" s="10"/>
-      <c r="V3" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:21" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V4" s="10"/>
-    </row>
-    <row r="5" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="B5" s="4">
         <v>8327</v>
@@ -805,14 +807,10 @@
       <c r="U5" s="4">
         <v>16</v>
       </c>
-      <c r="V5" s="4">
-        <f t="shared" ref="V5:V35" si="0">SUM(B5:U5)</f>
-        <v>77557</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="6">
         <v>5489</v>
@@ -874,14 +872,10 @@
       <c r="U6" s="6">
         <v>15</v>
       </c>
-      <c r="V6" s="6">
-        <f t="shared" si="0"/>
-        <v>54105</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="4">
         <v>5417</v>
@@ -943,14 +937,10 @@
       <c r="U7" s="4">
         <v>17</v>
       </c>
-      <c r="V7" s="4">
-        <f t="shared" si="0"/>
-        <v>47827</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="6">
         <v>9078</v>
@@ -1012,14 +1002,10 @@
       <c r="U8" s="6">
         <v>22</v>
       </c>
-      <c r="V8" s="6">
-        <f t="shared" si="0"/>
-        <v>85284</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="4">
         <v>5892</v>
@@ -1081,14 +1067,10 @@
       <c r="U9" s="4">
         <v>16</v>
       </c>
-      <c r="V9" s="4">
-        <f t="shared" si="0"/>
-        <v>60274</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="6">
         <v>6428</v>
@@ -1150,14 +1132,10 @@
       <c r="U10" s="6">
         <v>19</v>
       </c>
-      <c r="V10" s="6">
-        <f t="shared" si="0"/>
-        <v>60505</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="4">
         <v>12295</v>
@@ -1219,14 +1197,10 @@
       <c r="U11" s="4">
         <v>64</v>
       </c>
-      <c r="V11" s="4">
-        <f t="shared" si="0"/>
-        <v>121247</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="6">
         <v>14789</v>
@@ -1288,14 +1262,10 @@
       <c r="U12" s="6">
         <v>85</v>
       </c>
-      <c r="V12" s="6">
-        <f t="shared" si="0"/>
-        <v>116915</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="4">
         <v>11323</v>
@@ -1357,14 +1327,10 @@
       <c r="U13" s="4">
         <v>41</v>
       </c>
-      <c r="V13" s="4">
-        <f t="shared" si="0"/>
-        <v>91339</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="6">
         <v>13935</v>
@@ -1426,14 +1392,10 @@
       <c r="U14" s="6">
         <v>31</v>
       </c>
-      <c r="V14" s="6">
-        <f t="shared" si="0"/>
-        <v>143874</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="4">
         <v>17016</v>
@@ -1495,14 +1457,10 @@
       <c r="U15" s="4">
         <v>14</v>
       </c>
-      <c r="V15" s="4">
-        <f t="shared" si="0"/>
-        <v>169994</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="6">
         <v>6988</v>
@@ -1564,14 +1522,10 @@
       <c r="U16" s="6">
         <v>13</v>
       </c>
-      <c r="V16" s="6">
-        <f t="shared" si="0"/>
-        <v>62846</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="4">
         <v>8245</v>
@@ -1633,14 +1587,10 @@
       <c r="U17" s="4">
         <v>14</v>
       </c>
-      <c r="V17" s="4">
-        <f t="shared" si="0"/>
-        <v>74024</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="6">
         <v>8875</v>
@@ -1702,14 +1652,10 @@
       <c r="U18" s="6">
         <v>4</v>
       </c>
-      <c r="V18" s="6">
-        <f t="shared" si="0"/>
-        <v>61907</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="4">
         <v>7230</v>
@@ -1771,14 +1717,10 @@
       <c r="U19" s="4">
         <v>4</v>
       </c>
-      <c r="V19" s="4">
-        <f t="shared" si="0"/>
-        <v>66833</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="6">
         <v>11507</v>
@@ -1840,14 +1782,10 @@
       <c r="U20" s="6">
         <v>5</v>
       </c>
-      <c r="V20" s="6">
-        <f t="shared" si="0"/>
-        <v>96590</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="4">
         <v>13405</v>
@@ -1909,14 +1847,10 @@
       <c r="U21" s="4">
         <v>6</v>
       </c>
-      <c r="V21" s="4">
-        <f t="shared" si="0"/>
-        <v>108264</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="6">
         <v>30733</v>
@@ -1978,14 +1912,10 @@
       <c r="U22" s="6">
         <v>6</v>
       </c>
-      <c r="V22" s="6">
-        <f t="shared" si="0"/>
-        <v>216414</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="4">
         <v>9497</v>
@@ -2047,14 +1977,10 @@
       <c r="U23" s="4">
         <v>11</v>
       </c>
-      <c r="V23" s="4">
-        <f t="shared" si="0"/>
-        <v>108097</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="6">
         <v>6210</v>
@@ -2116,14 +2042,10 @@
       <c r="U24" s="6">
         <v>5</v>
       </c>
-      <c r="V24" s="6">
-        <f t="shared" si="0"/>
-        <v>63165</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="4">
         <v>36016</v>
@@ -2185,14 +2107,10 @@
       <c r="U25" s="4">
         <v>26</v>
       </c>
-      <c r="V25" s="4">
-        <f t="shared" si="0"/>
-        <v>239272</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="6">
         <v>24035</v>
@@ -2254,14 +2172,10 @@
       <c r="U26" s="6">
         <v>4</v>
       </c>
-      <c r="V26" s="6">
-        <f t="shared" si="0"/>
-        <v>179198</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="4">
         <v>6186</v>
@@ -2323,14 +2237,10 @@
       <c r="U27" s="4">
         <v>2</v>
       </c>
-      <c r="V27" s="4">
-        <f t="shared" si="0"/>
-        <v>46166</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="6">
         <v>12384</v>
@@ -2392,14 +2302,10 @@
       <c r="U28" s="6">
         <v>2</v>
       </c>
-      <c r="V28" s="6">
-        <f t="shared" si="0"/>
-        <v>104143</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="4">
         <v>24635</v>
@@ -2461,14 +2367,10 @@
       <c r="U29" s="4">
         <v>4</v>
       </c>
-      <c r="V29" s="4">
-        <f t="shared" si="0"/>
-        <v>206450</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="6">
         <v>9789</v>
@@ -2530,14 +2432,10 @@
       <c r="U30" s="6">
         <v>0</v>
       </c>
-      <c r="V30" s="6">
-        <f t="shared" si="0"/>
-        <v>85856</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="4">
         <v>11201</v>
@@ -2599,14 +2497,10 @@
       <c r="U31" s="4">
         <v>4</v>
       </c>
-      <c r="V31" s="4">
-        <f t="shared" si="0"/>
-        <v>107835</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" s="6">
         <v>18333</v>
@@ -2668,14 +2562,10 @@
       <c r="U32" s="6">
         <v>5</v>
       </c>
-      <c r="V32" s="6">
-        <f t="shared" si="0"/>
-        <v>126743</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33" s="4">
         <v>8244</v>
@@ -2737,14 +2627,10 @@
       <c r="U33" s="4">
         <v>0</v>
       </c>
-      <c r="V33" s="4">
-        <f t="shared" si="0"/>
-        <v>49808</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B34" s="6">
         <v>7117</v>
@@ -2806,14 +2692,10 @@
       <c r="U34" s="6">
         <v>2</v>
       </c>
-      <c r="V34" s="6">
-        <f t="shared" si="0"/>
-        <v>68351</v>
-      </c>
-    </row>
-    <row r="35" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:21" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B35" s="4">
         <v>7022</v>
@@ -2875,105 +2757,96 @@
       <c r="U35" s="4">
         <v>5</v>
       </c>
-      <c r="V35" s="4">
+    </row>
+    <row r="36" spans="1:21" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" s="8">
+        <f t="shared" ref="B36:U36" si="0">SUM(B5:B35)</f>
+        <v>377641</v>
+      </c>
+      <c r="C36" s="8">
         <f t="shared" si="0"/>
-        <v>58599</v>
-      </c>
-    </row>
-    <row r="36" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B36" s="8">
-        <f t="shared" ref="B36:V36" si="1">SUM(B5:B35)</f>
-        <v>377641</v>
-      </c>
-      <c r="C36" s="8">
-        <f t="shared" si="1"/>
         <v>362393</v>
       </c>
       <c r="D36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>118401</v>
       </c>
       <c r="E36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>114513</v>
       </c>
       <c r="F36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>222024</v>
       </c>
       <c r="G36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>285057</v>
       </c>
       <c r="H36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>193620</v>
       </c>
       <c r="I36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>205928</v>
       </c>
       <c r="J36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>464451</v>
       </c>
       <c r="K36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>426367</v>
       </c>
       <c r="L36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>9823</v>
       </c>
       <c r="M36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>10814</v>
       </c>
       <c r="N36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>17554</v>
       </c>
       <c r="O36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>22842</v>
       </c>
       <c r="P36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>153824</v>
       </c>
       <c r="Q36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>151491</v>
       </c>
       <c r="R36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>12602</v>
       </c>
       <c r="S36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>8757</v>
       </c>
       <c r="T36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>918</v>
       </c>
       <c r="U36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>462</v>
       </c>
-      <c r="V36" s="8">
-        <f t="shared" si="1"/>
-        <v>3159482</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="V3:V4"/>
     <mergeCell ref="R3:S3"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="T3:U3"/>
